--- a/ML-herb-recognition-DANE.xlsx
+++ b/ML-herb-recognition-DANE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasia\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasia\Desktop\ML-herb-recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E4DFD3-1C65-4F91-9772-21ABD5A0BE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548CD3C7-283D-474B-A963-48D69B6D940E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="0" windowWidth="14400" windowHeight="15750" firstSheet="8" activeTab="11" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="6252" firstSheet="11" activeTab="14" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Colors" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,14 @@
     <sheet name="Diseases" sheetId="10" r:id="rId10"/>
     <sheet name="ProductTypes" sheetId="11" r:id="rId11"/>
     <sheet name="Products" sheetId="12" r:id="rId12"/>
+    <sheet name="Poisonability" sheetId="13" r:id="rId13"/>
+    <sheet name="Saps" sheetId="14" r:id="rId14"/>
+    <sheet name="Roots" sheetId="15" r:id="rId15"/>
+    <sheet name="Stalks" sheetId="16" r:id="rId16"/>
+    <sheet name="Hats" sheetId="17" r:id="rId17"/>
+    <sheet name="Fruits" sheetId="19" r:id="rId18"/>
+    <sheet name="Flowers" sheetId="18" r:id="rId19"/>
+    <sheet name="Leafes" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="231">
   <si>
     <t>Id</t>
   </si>
@@ -621,6 +629,114 @@
   </si>
   <si>
     <t>gastric reflux (in excess)</t>
+  </si>
+  <si>
+    <t>May cause mild irritation or allergic reaction</t>
+  </si>
+  <si>
+    <t>Can cause nausea, vomiting or skin irritation</t>
+  </si>
+  <si>
+    <t>Toxic - causes serious symptoms like dizziness, strong vomiting, diarrhea</t>
+  </si>
+  <si>
+    <t>Highly toxic - can cause organ damage, breathing problems</t>
+  </si>
+  <si>
+    <t>Extremely toxic - can cause paralysis or death</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Occurance</t>
+  </si>
+  <si>
+    <t>ActiveSubstance</t>
+  </si>
+  <si>
+    <t>Symptoms</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>ActiveSubstanceId</t>
+  </si>
+  <si>
+    <t>DiseaseId</t>
+  </si>
+  <si>
+    <t>Recipe</t>
+  </si>
+  <si>
+    <t>HealthPrepertyId</t>
+  </si>
+  <si>
+    <t>Contraindication</t>
+  </si>
+  <si>
+    <t>ProductTypeId</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ColorId</t>
+  </si>
+  <si>
+    <t>LeavesStain</t>
+  </si>
+  <si>
+    <t>Sticky</t>
+  </si>
+  <si>
+    <t>Transparent</t>
+  </si>
+  <si>
+    <t>SurfaceId</t>
+  </si>
+  <si>
+    <t>ThicknessId</t>
+  </si>
+  <si>
+    <t>ShapeId</t>
+  </si>
+  <si>
+    <t>Colord</t>
+  </si>
+  <si>
+    <t>HasSpots</t>
+  </si>
+  <si>
+    <t>HasGills</t>
+  </si>
+  <si>
+    <t>FlavourId</t>
+  </si>
+  <si>
+    <t>SizeInCm</t>
+  </si>
+  <si>
+    <t>ScentPower</t>
+  </si>
+  <si>
+    <t>Stripes</t>
+  </si>
+  <si>
+    <t>Spots</t>
+  </si>
+  <si>
+    <t>Holes</t>
+  </si>
+  <si>
+    <t>LeafShapeId</t>
+  </si>
+  <si>
+    <t>LeafColorId</t>
+  </si>
+  <si>
+    <t>Length</t>
   </si>
 </sst>
 </file>
@@ -1169,8 +1285,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE7099B-A5EE-4FEF-AF3C-A70CEA02357C}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1656,6 +1775,23 @@
         <v>0</v>
       </c>
       <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28">
+        <v>255</v>
+      </c>
+      <c r="D28">
+        <v>255</v>
+      </c>
+      <c r="E28">
+        <v>255</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1664,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD69ACC-7089-4C80-BCCC-8DD32D0E1BE1}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
@@ -1672,167 +1808,178 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>145</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>160</v>
       </c>
     </row>
@@ -1843,86 +1990,94 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C958BD-C3BB-4904-95E2-B63C538D4002}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>170</v>
       </c>
     </row>
@@ -1933,87 +2088,87 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0106E1-19BC-432B-BBC0-1EE795D91FB1}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1">
-        <v>14</v>
+        <v>207</v>
+      </c>
+      <c r="D1" t="s">
+        <v>208</v>
       </c>
       <c r="E1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F1">
-        <v>4</v>
+        <v>209</v>
+      </c>
+      <c r="F1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3">
         <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -2021,19 +2176,1183 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB4CD88-D179-43E7-BB63-6B824B86F15A}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C5" t="s">
-        <v>187</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076C40C8-EF65-4769-AF79-AA7EEC1E1443}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB5C179-228C-4CB2-B374-262D26063ABD}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367B381E-38AC-4871-B3A2-9E2A1FF070AB}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8B1E79-47AC-47D7-AA16-C4544973F7C8}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>24</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2613C7F2-C6FE-4D63-BAFE-9347DB4EFFBF}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>21</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656FEA14-A5E7-4F2E-8444-7E710722E66F}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
       </c>
       <c r="D5">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
-        <v>188</v>
+      <c r="E5">
+        <v>13</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2041,62 +3360,122 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" t="s">
-        <v>189</v>
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>190</v>
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" t="s">
-        <v>191</v>
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>192</v>
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>194</v>
+      <c r="E8">
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2267,6 +3646,335 @@
       </c>
       <c r="B20" t="s">
         <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF5D3C7-25A6-4106-B925-CEC58F390415}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>21</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>12</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>25</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>12</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2541,30 +4249,38 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9445F368-8D53-4A3D-8CAF-659CA5173E8A}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2575,121 +4291,129 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEE78D5-2CDE-41DE-9483-E092B1F07510}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2700,169 +4424,177 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C715A7-525F-48C4-8B06-D2CEA214127A}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2873,175 +4605,235 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5036F7A8-2D27-4F40-A907-03AB38823BF9}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>116</v>
       </c>
-      <c r="C1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>117</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>118</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>119</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>120</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>121</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>122</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>123</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>124</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>125</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>126</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>127</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>128</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>129</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>130</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>16</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ML-herb-recognition-DANE.xlsx
+++ b/ML-herb-recognition-DANE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasia\Desktop\ML-herb-recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548CD3C7-283D-474B-A963-48D69B6D940E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C8FA92-4984-40FB-82AE-C8B7B5733F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="6252" firstSheet="11" activeTab="14" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="930" firstSheet="1" activeTab="1" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Colors" sheetId="1" r:id="rId1"/>
@@ -19,20 +19,23 @@
     <sheet name="Surfaces" sheetId="4" r:id="rId4"/>
     <sheet name="Thicknesses" sheetId="5" r:id="rId5"/>
     <sheet name="Types" sheetId="6" r:id="rId6"/>
-    <sheet name="Occurances" sheetId="7" r:id="rId7"/>
-    <sheet name="ActiveSubstances" sheetId="8" r:id="rId8"/>
-    <sheet name="HealthPorperties" sheetId="9" r:id="rId9"/>
-    <sheet name="Diseases" sheetId="10" r:id="rId10"/>
-    <sheet name="ProductTypes" sheetId="11" r:id="rId11"/>
-    <sheet name="Products" sheetId="12" r:id="rId12"/>
-    <sheet name="Poisonability" sheetId="13" r:id="rId13"/>
-    <sheet name="Saps" sheetId="14" r:id="rId14"/>
-    <sheet name="Roots" sheetId="15" r:id="rId15"/>
-    <sheet name="Stalks" sheetId="16" r:id="rId16"/>
-    <sheet name="Hats" sheetId="17" r:id="rId17"/>
+    <sheet name="ActiveSubstances" sheetId="8" r:id="rId7"/>
+    <sheet name="Diseases" sheetId="10" r:id="rId8"/>
+    <sheet name="ProductTypes" sheetId="11" r:id="rId9"/>
+    <sheet name="Products" sheetId="12" r:id="rId10"/>
+    <sheet name="Saps" sheetId="14" r:id="rId11"/>
+    <sheet name="Roots" sheetId="15" r:id="rId12"/>
+    <sheet name="Stalks" sheetId="16" r:id="rId13"/>
+    <sheet name="Occurances" sheetId="7" r:id="rId14"/>
+    <sheet name="Hats" sheetId="17" r:id="rId15"/>
+    <sheet name="Leafes" sheetId="20" r:id="rId16"/>
+    <sheet name="Flowers" sheetId="18" r:id="rId17"/>
     <sheet name="Fruits" sheetId="19" r:id="rId18"/>
-    <sheet name="Flowers" sheetId="18" r:id="rId19"/>
-    <sheet name="Leafes" sheetId="20" r:id="rId20"/>
+    <sheet name="Poisonability" sheetId="13" r:id="rId19"/>
+    <sheet name="Plants" sheetId="21" r:id="rId20"/>
+    <sheet name="PicturesId" sheetId="22" r:id="rId21"/>
+    <sheet name="HealthPorperties" sheetId="9" r:id="rId22"/>
+    <sheet name="PlantsProducts" sheetId="24" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="304">
   <si>
     <t>Id</t>
   </si>
@@ -559,12 +562,6 @@
     <t>Compress</t>
   </si>
   <si>
-    <t>Tansy ointment</t>
-  </si>
-  <si>
-    <t>Green walnut tincture</t>
-  </si>
-  <si>
     <t>Dandelion syrup</t>
   </si>
   <si>
@@ -577,24 +574,9 @@
     <t>Nettle juice</t>
   </si>
   <si>
-    <t>Garlic extract</t>
-  </si>
-  <si>
     <t>Mint tea blend</t>
   </si>
   <si>
-    <t>Dry tansy flowers, mix with warm oil and beeswax, heat gently, strain and let it solidify.</t>
-  </si>
-  <si>
-    <t>pregnancy, sensitive skin, allergies</t>
-  </si>
-  <si>
-    <t>Chop unripe green walnuts, pour alcohol over them, store in a dark place for 2-3 weeks, then strain.</t>
-  </si>
-  <si>
-    <t>stomach ulcers, pregnancy, alcohol sensitivity</t>
-  </si>
-  <si>
     <t>Boil dandelion flowers in water, strain, add sugar and lemon juice, simmer until thick.</t>
   </si>
   <si>
@@ -619,12 +601,6 @@
     <t>kidney disorders, pregnancy</t>
   </si>
   <si>
-    <t>Crush garlic and soak in alcohol or oil for several days, then strain</t>
-  </si>
-  <si>
-    <t>stomach irritation, blood thinning medication</t>
-  </si>
-  <si>
     <t>Mix dried mint leaves with other herbs, pour hot water and steep</t>
   </si>
   <si>
@@ -737,16 +713,271 @@
   </si>
   <si>
     <t>Length</t>
+  </si>
+  <si>
+    <t>LatinName</t>
+  </si>
+  <si>
+    <t>Subriquet</t>
+  </si>
+  <si>
+    <t>TypeId</t>
+  </si>
+  <si>
+    <t>SapId</t>
+  </si>
+  <si>
+    <t>RootId</t>
+  </si>
+  <si>
+    <t>OccuranceId</t>
+  </si>
+  <si>
+    <t>HatId</t>
+  </si>
+  <si>
+    <t>LeafId</t>
+  </si>
+  <si>
+    <t>FlowerId</t>
+  </si>
+  <si>
+    <t>FruitId</t>
+  </si>
+  <si>
+    <t>SimilarPlantsId</t>
+  </si>
+  <si>
+    <t>PoisonabilityId</t>
+  </si>
+  <si>
+    <t>Birch</t>
+  </si>
+  <si>
+    <t>PolishName</t>
+  </si>
+  <si>
+    <t>StalkId</t>
+  </si>
+  <si>
+    <t>Brzoza</t>
+  </si>
+  <si>
+    <t>Betula pendula</t>
+  </si>
+  <si>
+    <t>PictureLink</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Illustration_Betula_pendula_very_clean.jpg/960px-Illustration_Betula_pendula_very_clean.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/B._pendula%2C_Koivu_Birch_end_of_Sept.jpg/960px-B._pendula%2C_Koivu_Birch_end_of_Sept.jpg</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>Pine</t>
+  </si>
+  <si>
+    <t>Dandelion</t>
+  </si>
+  <si>
+    <t>Aloe</t>
+  </si>
+  <si>
+    <t>Chanterelle</t>
+  </si>
+  <si>
+    <t>Fly agaric</t>
+  </si>
+  <si>
+    <t>Champigon</t>
+  </si>
+  <si>
+    <t>Nettle</t>
+  </si>
+  <si>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>Chamomile</t>
+  </si>
+  <si>
+    <t>Sosna</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/0b/Pinus_sylvestris_-_Köhler–s_Medizinal-Pflanzen-106.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Pinus_sylvestris_branch.jpg/960px-Pinus_sylvestris_branch.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Sosna_na_Sokolicy_1_wykadrowane.JPG/960px-Sosna_na_Sokolicy_1_wykadrowane.JPG</t>
+  </si>
+  <si>
+    <t>Pinus sylvestris</t>
+  </si>
+  <si>
+    <t>Mniszek pospolity</t>
+  </si>
+  <si>
+    <t>Mniszek lekarski</t>
+  </si>
+  <si>
+    <t>Taraxacum officinale</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Taraxacum_officinale_-_Köhler–s_Medizinal-Pflanzen-135.jpg/960px-Taraxacum_officinale_-_Köhler–s_Medizinal-Pflanzen-135.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ee/Smetanka_lékařská.JPG/960px-Smetanka_lékařská.JPG</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4b/Löwenzahnblüte_im_Frühling0003.JPG/960px-Löwenzahnblüte_im_Frühling0003.JPG</t>
+  </si>
+  <si>
+    <t>Aloes</t>
+  </si>
+  <si>
+    <t>Aloe vera</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2e/Aloe_vera%2C_Jardín_Botánico%2C_Múnich%2C_Alemania_2012-04-21%2C_DD_01.JPG/960px-Aloe_vera%2C_Jardín_Botánico%2C_Múnich%2C_Alemania_2012-04-21%2C_DD_01.JPG</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Fuerteventura_Aloe_Vera.jpg/960px-Fuerteventura_Aloe_Vera.jpg</t>
+  </si>
+  <si>
+    <t>https://klubpodaloesem.pl/wp-content/uploads/2020/06/botanical-drawings-botanical-illustration.jpg</t>
+  </si>
+  <si>
+    <t>Kurka</t>
+  </si>
+  <si>
+    <t>Pieprznik jadalny</t>
+  </si>
+  <si>
+    <t>Cantharellus cibarius</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/Cantharellus_cibarius_20090717-02.jpg/960px-Cantharellus_cibarius_20090717-02.jpg</t>
+  </si>
+  <si>
+    <t>https://cudnapolska.pl/wp-content/uploads/2024/04/Pieprznik-ametystowy-przekroj.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Amanita_muscaria_3_vliegenzwammen_op_rij.jpg/960px-Amanita_muscaria_3_vliegenzwammen_op_rij.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Amanita_muscaria_section_1_WF_orig.jpg/960px-Amanita_muscaria_section_1_WF_orig.jpg</t>
+  </si>
+  <si>
+    <t>Muchomor czerwony</t>
+  </si>
+  <si>
+    <t>Amanita muscaria</t>
+  </si>
+  <si>
+    <t>Pieczarka</t>
+  </si>
+  <si>
+    <t>Pieczarka dwuzarodnikowa</t>
+  </si>
+  <si>
+    <t>Agaricus bisporus</t>
+  </si>
+  <si>
+    <t>Pokrzywa zwyczajna</t>
+  </si>
+  <si>
+    <t>Pokrzywa</t>
+  </si>
+  <si>
+    <t>Urtica dioica</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c6/Agaricus_bisporus_G4.JPG/960px-Agaricus_bisporus_G4.JPG</t>
+  </si>
+  <si>
+    <t>https://us.123rf.com/450wm/kirpmun/kirpmun1805/kirpmun180500019/100729700-champignon-mushroom-hand-drawn-sketch-illustration.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Brennnessel_1.JPG/960px-Brennnessel_1.JPG</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Urtica_dioica_kz17.jpg/960px-Urtica_dioica_kz17.jpg</t>
+  </si>
+  <si>
+    <t>Mięta pieprzowa</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/49/Mentha_×_piperita_-_Köhler–s_Medizinal-Pflanzen-095.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/0d/Mentha-piperita.JPG</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSt-87bSr1CdFM2OZkHgr0o1FuWKZ4eNXt-YlrS3mGetIxWrX9gF8x_vNP2cZQRRIupAiDeq8Des3jfO7PS2hegbO-wl2BrPPcO4xIQJBU&amp;s=10</t>
+  </si>
+  <si>
+    <t>Mentha piperita</t>
+  </si>
+  <si>
+    <t>Rumianek</t>
+  </si>
+  <si>
+    <t>Matricaria </t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c7/Matricaria_recutita_-_Köhler–s_Medizinal-Pflanzen-091.jpg/960px-Matricaria_recutita_-_Köhler–s_Medizinal-Pflanzen-091.jpg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Atlas_roslin_pl_Rumianek_pospolity_2097_7384.jpg/960px-Atlas_roslin_pl_Rumianek_pospolity_2097_7384.jpg</t>
+  </si>
+  <si>
+    <t>PlantsId</t>
+  </si>
+  <si>
+    <t>in pots inside</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>FlavoursId</t>
+  </si>
+  <si>
+    <t>https://images.immediate.co.uk/production/volatile/sites/63/2024/08/ff8e4324ecdc5d98c32d405ec76cf431b1550108-a8c902d.jpeg?quality=90&amp;resize=800,534</t>
+  </si>
+  <si>
+    <t>PlantId</t>
+  </si>
+  <si>
+    <t>ProductId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -926,10 +1157,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -957,14 +1189,17 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF32CD32"/>
       <color rgb="FF800020"/>
       <color rgb="FF000000"/>
       <color rgb="FF404040"/>
@@ -972,7 +1207,6 @@
       <color rgb="FFD2B48C"/>
       <color rgb="FF654321"/>
       <color rgb="FF8B4513"/>
-      <color rgb="FF32CD32"/>
       <color rgb="FF6B8E23"/>
       <color rgb="FF00CC00"/>
     </mruColors>
@@ -1781,7 +2015,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C28">
         <v>255</v>
@@ -1799,188 +2033,138 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD69ACC-7089-4C80-BCCC-8DD32D0E1BE1}">
-  <dimension ref="A1:C16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0106E1-19BC-432B-BBC0-1EE795D91FB1}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" t="s">
         <v>200</v>
       </c>
-      <c r="C1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+        <v>184</v>
+      </c>
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" t="s">
-        <v>160</v>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1989,357 +2173,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C958BD-C3BB-4904-95E2-B63C538D4002}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0106E1-19BC-432B-BBC0-1EE795D91FB1}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB4CD88-D179-43E7-BB63-6B824B86F15A}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076C40C8-EF65-4769-AF79-AA7EEC1E1443}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
@@ -2353,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2384,7 +2219,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2395,7 +2230,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2409,68 +2244,12 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
         <v>1</v>
       </c>
     </row>
@@ -2479,9 +2258,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB5C179-228C-4CB2-B374-262D26063ABD}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
@@ -2495,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,13 +2288,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,13 +2316,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2551,13 +2330,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,10 +2344,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -2585,7 +2364,115 @@
         <v>1</v>
       </c>
       <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367B381E-38AC-4871-B3A2-9E2A1FF070AB}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2593,13 +2480,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -2607,13 +2494,256 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEE78D5-2CDE-41DE-9483-E092B1F07510}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8B1E79-47AC-47D7-AA16-C4544973F7C8}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2622,134 +2752,267 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367B381E-38AC-4871-B3A2-9E2A1FF070AB}">
-  <dimension ref="A1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF5D3C7-25A6-4106-B925-CEC58F390415}">
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1" t="s">
         <v>218</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>219</v>
       </c>
-      <c r="D1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
         <v>21</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>9</v>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2758,261 +3021,168 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8B1E79-47AC-47D7-AA16-C4544973F7C8}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656FEA14-A5E7-4F2E-8444-7E710722E66F}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="D1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>242</v>
       </c>
       <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>242</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>298</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>242</v>
       </c>
       <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>24</v>
+      <c r="B7" t="s">
+        <v>299</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
         <v>3</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3022,7 +3192,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2613C7F2-C6FE-4D63-BAFE-9347DB4EFFBF}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3033,218 +3203,118 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>242</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="B3" t="s">
+        <v>242</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="s">
+        <v>242</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>242</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>23</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>8</v>
-      </c>
-      <c r="D11">
-        <v>11</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
         <v>1</v>
       </c>
     </row>
@@ -3254,228 +3324,59 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656FEA14-A5E7-4F2E-8444-7E710722E66F}">
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB4CD88-D179-43E7-BB63-6B824B86F15A}">
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="60.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>8</v>
-      </c>
-      <c r="E8">
-        <v>16</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>15</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>14</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>8</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>16</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
+      <c r="B6" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3487,6 +3388,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711C130C-398C-48F7-B440-F4EF1EDFE1A8}">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3654,327 +3558,1219 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF5D3C7-25A6-4106-B925-CEC58F390415}">
-  <dimension ref="A1:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F7ADAA-D38B-4FD0-A7F1-B1E355747A12}">
+  <sheetPr>
+    <tabColor rgb="FF32CD32"/>
+  </sheetPr>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1" t="s">
+        <v>229</v>
+      </c>
+      <c r="M1" t="s">
+        <v>230</v>
+      </c>
+      <c r="N1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" t="s">
+        <v>232</v>
+      </c>
+      <c r="P1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>242</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>242</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>242</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>242</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>242</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M6" t="s">
+        <v>242</v>
+      </c>
+      <c r="N6" t="s">
+        <v>242</v>
+      </c>
+      <c r="O6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H7" t="s">
+        <v>242</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" t="s">
+        <v>242</v>
+      </c>
+      <c r="M7" t="s">
+        <v>242</v>
+      </c>
+      <c r="N7" t="s">
+        <v>242</v>
+      </c>
+      <c r="O7" t="s">
+        <v>242</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>242</v>
+      </c>
+      <c r="H8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M8" t="s">
+        <v>242</v>
+      </c>
+      <c r="N8" t="s">
+        <v>242</v>
+      </c>
+      <c r="O8" t="s">
+        <v>242</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>242</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9" t="s">
+        <v>242</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>242</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10" t="s">
+        <v>242</v>
+      </c>
+      <c r="L10">
+        <v>6</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>242</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>242</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>242</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+      <c r="O11" t="s">
+        <v>242</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45929B25-8F0F-4486-806B-5E96332ADC13}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{57938D44-22CE-4AFC-A97A-5D3BEB2CF2C2}"/>
+    <hyperlink ref="C23" r:id="rId2" xr:uid="{8CF6B935-9488-432E-8639-D2F39DFC6FB0}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{8AA697E7-BAC8-41C6-8566-EFA3B94DFD01}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{14955A7A-B2AD-44A8-AF59-234F73F392D3}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{8CFA290C-F7F4-43EB-A076-F5B630AE2D64}"/>
+    <hyperlink ref="C4" r:id="rId6" xr:uid="{50DE4638-9FAB-409F-BDAB-FE8B1CF0C5EF}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{937D2934-E2BB-4DA9-938E-3A4697A22DD6}"/>
+    <hyperlink ref="C7" r:id="rId8" xr:uid="{4B9DDEA4-64C0-4046-B040-6C56627A196C}"/>
+    <hyperlink ref="C8" r:id="rId9" xr:uid="{B81100F5-0588-458D-868C-A0ABE020004C}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{2EF0DC0D-46AE-4166-86FE-59F4D0BB0227}"/>
+    <hyperlink ref="C9" r:id="rId11" xr:uid="{C50A1138-0A95-42C5-99E7-0FF5B0B8B0C1}"/>
+    <hyperlink ref="C11" r:id="rId12" xr:uid="{8EF1183E-C48D-4296-ACD8-95CEF827CF6A}"/>
+    <hyperlink ref="C12" r:id="rId13" xr:uid="{71E94E27-F295-4217-81B4-5E049714E7B5}"/>
+    <hyperlink ref="C13" r:id="rId14" xr:uid="{6341F881-FF00-4596-A45B-DA0C04A7DEE1}"/>
+    <hyperlink ref="C14" r:id="rId15" xr:uid="{E093F323-DB33-42F0-A965-C2222912FAB8}"/>
+    <hyperlink ref="C15" r:id="rId16" xr:uid="{ACA344AB-D72F-4D43-9D27-5C404C8C6B51}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{8B95D708-E672-4CCA-A6AA-EA1DDB4889FB}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{6A9110AB-0F2B-49DD-A3D8-7EF1240C6847}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{E117A28E-BBDF-4ACB-B931-196579925E19}"/>
+    <hyperlink ref="C20" r:id="rId20" xr:uid="{FFD43FA9-3317-4C89-BD84-F84C2DFA1873}"/>
+    <hyperlink ref="C21" r:id="rId21" xr:uid="{BBF42AA3-8218-448B-9010-EBE88C9D2D1A}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{A531FA14-A22D-4886-ACA9-370E60C13E19}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{88F1F52D-2C86-465B-BE87-D14BA4A498CA}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{AB8DE681-7335-411D-9EF8-A40EA6CAAD3D}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{E015719A-0F25-4728-95AF-873D26608F69}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5036F7A8-2D27-4F40-A907-03AB38823BF9}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="8.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72F8277-2704-4BFD-BC4B-3D2AA1C3B4EA}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>225</v>
+        <v>302</v>
       </c>
       <c r="C1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G1" t="s">
-        <v>216</v>
-      </c>
-      <c r="H1" t="s">
-        <v>230</v>
-      </c>
-      <c r="I1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>21</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>21</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>25</v>
-      </c>
-      <c r="I9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>20</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>8</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>12</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4257,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -4290,139 +5086,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEE78D5-2CDE-41DE-9483-E092B1F07510}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C715A7-525F-48C4-8B06-D2CEA214127A}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4435,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -4596,6 +5259,196 @@
       </c>
       <c r="B21" t="s">
         <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD69ACC-7089-4C80-BCCC-8DD32D0E1BE1}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4604,236 +5457,96 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5036F7A8-2D27-4F40-A907-03AB38823BF9}">
-  <dimension ref="A1:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C958BD-C3BB-4904-95E2-B63C538D4002}">
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16">
-        <v>16</v>
-      </c>
-      <c r="D16">
-        <v>11</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/ML-herb-recognition-DANE.xlsx
+++ b/ML-herb-recognition-DANE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasia\Desktop\ML-herb-recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C8FA92-4984-40FB-82AE-C8B7B5733F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967790D5-4735-4227-A62F-F133B2EC31C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="930" firstSheet="1" activeTab="1" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
+    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15750" tabRatio="930" firstSheet="9" activeTab="10" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Colors" sheetId="1" r:id="rId1"/>
@@ -1519,6 +1519,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE7099B-A5EE-4FEF-AF3C-A70CEA02357C}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2260,6 +2263,9 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB5C179-228C-4CB2-B374-262D26063ABD}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2510,6 +2516,9 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEE78D5-2CDE-41DE-9483-E092B1F07510}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2651,6 +2660,9 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8B1E79-47AC-47D7-AA16-C4544973F7C8}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -2753,6 +2765,9 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF5D3C7-25A6-4106-B925-CEC58F390415}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3022,6 +3037,9 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656FEA14-A5E7-4F2E-8444-7E710722E66F}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3192,6 +3210,9 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2613C7F2-C6FE-4D63-BAFE-9347DB4EFFBF}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3386,6 +3407,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711C130C-398C-48F7-B440-F4EF1EDFE1A8}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4465,6 +4489,9 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5036F7A8-2D27-4F40-A907-03AB38823BF9}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4780,6 +4807,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13DE7AB-A127-4693-876C-B5F4C914E2E1}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4873,6 +4903,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D2D1C2-BC6F-49A2-914C-E738466089FA}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4971,6 +5004,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0D2913-F7D8-4615-A16A-1B5D75758C41}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -5087,6 +5123,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C715A7-525F-48C4-8B06-D2CEA214127A}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5268,6 +5307,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD69ACC-7089-4C80-BCCC-8DD32D0E1BE1}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/ML-herb-recognition-DANE.xlsx
+++ b/ML-herb-recognition-DANE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasia\Desktop\ML-herb-recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967790D5-4735-4227-A62F-F133B2EC31C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5EDE1-D502-4A01-A250-55A394218927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15750" tabRatio="930" firstSheet="9" activeTab="10" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="930" firstSheet="7" activeTab="22" xr2:uid="{54BFF693-94BF-4C22-9B72-2C8DB4535EB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Colors" sheetId="1" r:id="rId1"/>
@@ -2038,7 +2038,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0106E1-19BC-432B-BBC0-1EE795D91FB1}">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2177,6 +2177,9 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076C40C8-EF65-4769-AF79-AA7EEC1E1443}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2380,6 +2383,9 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367B381E-38AC-4871-B3A2-9E2A1FF070AB}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3346,6 +3352,9 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB4CD88-D179-43E7-BB63-6B824B86F15A}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3584,7 +3593,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F7ADAA-D38B-4FD0-A7F1-B1E355747A12}">
   <sheetPr>
-    <tabColor rgb="FF32CD32"/>
+    <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4163,6 +4172,9 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45929B25-8F0F-4486-806B-5E96332ADC13}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5081,6 +5093,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9445F368-8D53-4A3D-8CAF-659CA5173E8A}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -5500,6 +5515,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C958BD-C3BB-4904-95E2-B63C538D4002}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
